--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/113.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/113.xlsx
@@ -426,13 +426,13 @@
         <v>-18.80192134958295</v>
       </c>
       <c r="E2">
-        <v>-23.26356801660063</v>
+        <v>-19.5024696793718</v>
       </c>
       <c r="F2">
-        <v>-3.446552780277091</v>
+        <v>-2.072236586784126</v>
       </c>
       <c r="G2">
-        <v>-17.07553659821079</v>
+        <v>-17.02455919932471</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.48533398225281</v>
       </c>
       <c r="E3">
-        <v>-24.36797751246506</v>
+        <v>-20.00747110399167</v>
       </c>
       <c r="F3">
-        <v>-3.579973776008993</v>
+        <v>-2.070241878078185</v>
       </c>
       <c r="G3">
-        <v>-16.82322249257494</v>
+        <v>-16.84082674335282</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.12959178401946</v>
       </c>
       <c r="E4">
-        <v>-24.41759592816278</v>
+        <v>-20.11286714778185</v>
       </c>
       <c r="F4">
-        <v>-3.717165500158438</v>
+        <v>-2.158096868084295</v>
       </c>
       <c r="G4">
-        <v>-16.91311042884697</v>
+        <v>-16.20437812155893</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.78390877089767</v>
       </c>
       <c r="E5">
-        <v>-23.7902824300267</v>
+        <v>-20.94252510166357</v>
       </c>
       <c r="F5">
-        <v>-2.279512335047424</v>
+        <v>-2.063981077247826</v>
       </c>
       <c r="G5">
-        <v>-16.38024048796091</v>
+        <v>-15.96219631568119</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.43275967250172</v>
       </c>
       <c r="E6">
-        <v>-23.53303667377815</v>
+        <v>-21.19938460925892</v>
       </c>
       <c r="F6">
-        <v>-2.940965362917634</v>
+        <v>-1.808015549782779</v>
       </c>
       <c r="G6">
-        <v>-16.47934304726727</v>
+        <v>-15.85461405794289</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.09974697037381</v>
       </c>
       <c r="E7">
-        <v>-25.91726654581115</v>
+        <v>-22.31313467739289</v>
       </c>
       <c r="F7">
-        <v>-3.426425109123868</v>
+        <v>-1.99981988006399</v>
       </c>
       <c r="G7">
-        <v>-15.59838122467578</v>
+        <v>-15.34097616708726</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.79065577973862</v>
       </c>
       <c r="E8">
-        <v>-24.54746269307885</v>
+        <v>-22.41631705954693</v>
       </c>
       <c r="F8">
-        <v>-2.861854619215476</v>
+        <v>-1.739945286825132</v>
       </c>
       <c r="G8">
-        <v>-15.82510089571265</v>
+        <v>-14.88691546780084</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.51663437041028</v>
       </c>
       <c r="E9">
-        <v>-24.14141983469566</v>
+        <v>-23.42898211724589</v>
       </c>
       <c r="F9">
-        <v>-2.523467363539281</v>
+        <v>-1.544491998134589</v>
       </c>
       <c r="G9">
-        <v>-15.50133332136262</v>
+        <v>-14.7563704060114</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.2886670665744</v>
       </c>
       <c r="E10">
-        <v>-25.07564734331391</v>
+        <v>-23.97729322956108</v>
       </c>
       <c r="F10">
-        <v>-2.936610635481117</v>
+        <v>-1.820244737750308</v>
       </c>
       <c r="G10">
-        <v>-15.64387605992052</v>
+        <v>-13.96721150084952</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.10245502799701</v>
       </c>
       <c r="E11">
-        <v>-24.4691372807039</v>
+        <v>-23.63467821453068</v>
       </c>
       <c r="F11">
-        <v>-2.067851209753705</v>
+        <v>-1.641959363482784</v>
       </c>
       <c r="G11">
-        <v>-14.72549051898771</v>
+        <v>-13.96984443676966</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.97585271123287</v>
       </c>
       <c r="E12">
-        <v>-28.05218121862035</v>
+        <v>-23.793393185309</v>
       </c>
       <c r="F12">
-        <v>-2.006197480698144</v>
+        <v>-1.524889511914741</v>
       </c>
       <c r="G12">
-        <v>-14.94023078846826</v>
+        <v>-13.76453026063533</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.89504524212607</v>
       </c>
       <c r="E13">
-        <v>-27.67329413248455</v>
+        <v>-25.15462896307818</v>
       </c>
       <c r="F13">
-        <v>-2.429266250860324</v>
+        <v>-1.57810052040097</v>
       </c>
       <c r="G13">
-        <v>-14.08977682179622</v>
+        <v>-13.09440694973296</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.87952508752618</v>
       </c>
       <c r="E14">
-        <v>-30.30710500926613</v>
+        <v>-26.65600655058105</v>
       </c>
       <c r="F14">
-        <v>-1.783649950996834</v>
+        <v>-1.018491122867945</v>
       </c>
       <c r="G14">
-        <v>-12.7138609020154</v>
+        <v>-12.50736014246441</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.90177262018844</v>
       </c>
       <c r="E15">
-        <v>-28.46338859528596</v>
+        <v>-26.8400851829201</v>
       </c>
       <c r="F15">
-        <v>-2.054204685159986</v>
+        <v>-1.059829969737251</v>
       </c>
       <c r="G15">
-        <v>-12.45551858711867</v>
+        <v>-12.11939044250202</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.95464426781761</v>
       </c>
       <c r="E16">
-        <v>-30.45793095513294</v>
+        <v>-27.66671959895735</v>
       </c>
       <c r="F16">
-        <v>-1.609541205174225</v>
+        <v>-0.790436606672824</v>
       </c>
       <c r="G16">
-        <v>-13.36495188484855</v>
+        <v>-12.17738030135983</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.99261986044469</v>
       </c>
       <c r="E17">
-        <v>-29.40259995749401</v>
+        <v>-28.11569835601661</v>
       </c>
       <c r="F17">
-        <v>-1.911920986585532</v>
+        <v>-0.6415168568345428</v>
       </c>
       <c r="G17">
-        <v>-13.18467605471529</v>
+        <v>-12.09419806257007</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.98806606036989</v>
       </c>
       <c r="E18">
-        <v>-31.48202149718652</v>
+        <v>-28.85514025350041</v>
       </c>
       <c r="F18">
-        <v>-1.132559799335645</v>
+        <v>-0.3249330595674334</v>
       </c>
       <c r="G18">
-        <v>-13.55585605621223</v>
+        <v>-11.32994174469052</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.9072502453182</v>
       </c>
       <c r="E19">
-        <v>-30.76874483104914</v>
+        <v>-29.39225846129519</v>
       </c>
       <c r="F19">
-        <v>-1.17194535586915</v>
+        <v>-0.499867687690633</v>
       </c>
       <c r="G19">
-        <v>-12.40965563688659</v>
+        <v>-10.90574404740955</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.72915336652364</v>
       </c>
       <c r="E20">
-        <v>-33.11780530958348</v>
+        <v>-30.42037346512252</v>
       </c>
       <c r="F20">
-        <v>-0.451560614228977</v>
+        <v>-0.08946465511725715</v>
       </c>
       <c r="G20">
-        <v>-12.4212251515421</v>
+        <v>-11.00686079616796</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.45019819958393</v>
       </c>
       <c r="E21">
-        <v>-33.54177342804463</v>
+        <v>-30.84577028827941</v>
       </c>
       <c r="F21">
-        <v>-0.8977607157469307</v>
+        <v>-0.04353168263202457</v>
       </c>
       <c r="G21">
-        <v>-12.74556578432988</v>
+        <v>-10.82057242124137</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-15.06852516039871</v>
       </c>
       <c r="E22">
-        <v>-34.80987136524887</v>
+        <v>-31.51496061620373</v>
       </c>
       <c r="F22">
-        <v>-0.3413363908776693</v>
+        <v>0.305340219261404</v>
       </c>
       <c r="G22">
-        <v>-12.13886920789631</v>
+        <v>-10.71235966868431</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.61000079310573</v>
       </c>
       <c r="E23">
-        <v>-33.94174636807658</v>
+        <v>-31.59953453501688</v>
       </c>
       <c r="F23">
-        <v>-0.6881522848773495</v>
+        <v>0.6725447201461885</v>
       </c>
       <c r="G23">
-        <v>-12.25637621119773</v>
+        <v>-10.65190657230479</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.07826869580962</v>
       </c>
       <c r="E24">
-        <v>-34.75915442515572</v>
+        <v>-31.72168670989707</v>
       </c>
       <c r="F24">
-        <v>-0.4177582539903404</v>
+        <v>0.3713188545269818</v>
       </c>
       <c r="G24">
-        <v>-12.06207154500413</v>
+        <v>-10.62230333938615</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.5085061221004</v>
       </c>
       <c r="E25">
-        <v>-35.76215288349616</v>
+        <v>-31.811576739206</v>
       </c>
       <c r="F25">
-        <v>-0.9587368402670023</v>
+        <v>0.4235880092762279</v>
       </c>
       <c r="G25">
-        <v>-11.99365437224941</v>
+        <v>-10.42984838573535</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.90982580790575</v>
       </c>
       <c r="E26">
-        <v>-33.89790714593735</v>
+        <v>-32.35731909031678</v>
       </c>
       <c r="F26">
-        <v>-0.3607458674926645</v>
+        <v>0.363393863584399</v>
       </c>
       <c r="G26">
-        <v>-12.3763947507958</v>
+        <v>-10.79745036177017</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.32213910275085</v>
       </c>
       <c r="E27">
-        <v>-34.37863305036361</v>
+        <v>-32.20832886385554</v>
       </c>
       <c r="F27">
-        <v>-0.4757373452470834</v>
+        <v>0.5575433019829359</v>
       </c>
       <c r="G27">
-        <v>-13.17082344391485</v>
+        <v>-10.71162474408191</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.76370564038485</v>
       </c>
       <c r="E28">
-        <v>-34.86430127626641</v>
+        <v>-31.61706316341331</v>
       </c>
       <c r="F28">
-        <v>-0.3672319842565846</v>
+        <v>0.4229186884147658</v>
       </c>
       <c r="G28">
-        <v>-11.57130508213895</v>
+        <v>-10.8178885758017</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.26769016831177</v>
       </c>
       <c r="E29">
-        <v>-33.07439179160505</v>
+        <v>-32.16967492605536</v>
       </c>
       <c r="F29">
-        <v>-0.5029301619787828</v>
+        <v>0.4308975232385307</v>
       </c>
       <c r="G29">
-        <v>-12.20158320909174</v>
+        <v>-10.59079948440519</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.85064537607467</v>
       </c>
       <c r="E30">
-        <v>-33.53189501490853</v>
+        <v>-31.7285748108793</v>
       </c>
       <c r="F30">
-        <v>-0.5676712163445782</v>
+        <v>0.3964887980610448</v>
       </c>
       <c r="G30">
-        <v>-13.31458540019679</v>
+        <v>-10.6444111245837</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.52395850273486</v>
       </c>
       <c r="E31">
-        <v>-33.79642342721517</v>
+        <v>-31.44865252079718</v>
       </c>
       <c r="F31">
-        <v>-1.610398565436123</v>
+        <v>0.263420686842735</v>
       </c>
       <c r="G31">
-        <v>-13.30277047554971</v>
+        <v>-10.90201329338885</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.29329781420505</v>
       </c>
       <c r="E32">
-        <v>-34.71292710650472</v>
+        <v>-31.74735355588451</v>
       </c>
       <c r="F32">
-        <v>-0.6890021898326217</v>
+        <v>0.2267993923323717</v>
       </c>
       <c r="G32">
-        <v>-12.30313203607998</v>
+        <v>-10.79154746824966</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.14701811642708</v>
       </c>
       <c r="E33">
-        <v>-34.54822112839033</v>
+        <v>-31.25465601981444</v>
       </c>
       <c r="F33">
-        <v>-0.4744558608749526</v>
+        <v>0.3465415571418458</v>
       </c>
       <c r="G33">
-        <v>-13.25616085236457</v>
+        <v>-10.87904918396542</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.08435781797065</v>
       </c>
       <c r="E34">
-        <v>-34.15080033671749</v>
+        <v>-30.51338670934772</v>
       </c>
       <c r="F34">
-        <v>-0.8695556340490104</v>
+        <v>0.5240466093159323</v>
       </c>
       <c r="G34">
-        <v>-12.49094508584778</v>
+        <v>-10.8529378219374</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.07928575070502</v>
       </c>
       <c r="E35">
-        <v>-33.82675432952039</v>
+        <v>-30.50259666632581</v>
       </c>
       <c r="F35">
-        <v>-0.9202715999180073</v>
+        <v>0.00902822907560406</v>
       </c>
       <c r="G35">
-        <v>-12.26069438275143</v>
+        <v>-11.0331118330316</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.13134888318884</v>
       </c>
       <c r="E36">
-        <v>-33.33431013934113</v>
+        <v>-29.79522379008668</v>
       </c>
       <c r="F36">
-        <v>-0.5186558887535286</v>
+        <v>0.5316038051316722</v>
       </c>
       <c r="G36">
-        <v>-11.75676193491327</v>
+        <v>-11.29782305935835</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.2135151217317</v>
       </c>
       <c r="E37">
-        <v>-32.65245667008741</v>
+        <v>-29.96099506690588</v>
       </c>
       <c r="F37">
-        <v>-0.06127945423700398</v>
+        <v>0.3032767560610304</v>
       </c>
       <c r="G37">
-        <v>-12.90480423454795</v>
+        <v>-10.77226189795511</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.32983316055849</v>
       </c>
       <c r="E38">
-        <v>-31.21803923216909</v>
+        <v>-30.10832608544285</v>
       </c>
       <c r="F38">
-        <v>-0.1115704676283648</v>
+        <v>0.3547755291256729</v>
       </c>
       <c r="G38">
-        <v>-11.47516049645431</v>
+        <v>-11.13699597105659</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.46318708372258</v>
       </c>
       <c r="E39">
-        <v>-31.68581957689585</v>
+        <v>-29.23718378024308</v>
       </c>
       <c r="F39">
-        <v>-0.4810968823431962</v>
+        <v>0.706888832666256</v>
       </c>
       <c r="G39">
-        <v>-13.42385028282407</v>
+        <v>-11.34380479846934</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.62127292260325</v>
       </c>
       <c r="E40">
-        <v>-29.95328463008134</v>
+        <v>-28.27557414936022</v>
       </c>
       <c r="F40">
-        <v>0.3069248861029595</v>
+        <v>0.5988117376230044</v>
       </c>
       <c r="G40">
-        <v>-13.17527476344269</v>
+        <v>-11.29725783315438</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.79812903076829</v>
       </c>
       <c r="E41">
-        <v>-31.81640692397677</v>
+        <v>-28.24672802010363</v>
       </c>
       <c r="F41">
-        <v>-0.2986133420782847</v>
+        <v>0.9499724186503681</v>
       </c>
       <c r="G41">
-        <v>-13.48019406721718</v>
+        <v>-11.4100615800749</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.99961156325841</v>
       </c>
       <c r="E42">
-        <v>-31.27923057122345</v>
+        <v>-27.85522140135734</v>
       </c>
       <c r="F42">
-        <v>-0.5737920230838637</v>
+        <v>0.41737773885744</v>
       </c>
       <c r="G42">
-        <v>-12.59196393168403</v>
+        <v>-11.58899026599915</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.2276692919776</v>
       </c>
       <c r="E43">
-        <v>-29.20475965943014</v>
+        <v>-26.57336595163961</v>
       </c>
       <c r="F43">
-        <v>-0.4246709799667023</v>
+        <v>0.5394484444361834</v>
       </c>
       <c r="G43">
-        <v>-12.68804194338159</v>
+        <v>-11.33258512358903</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.48197335073219</v>
       </c>
       <c r="E44">
-        <v>-29.74521497252442</v>
+        <v>-26.99002857138039</v>
       </c>
       <c r="F44">
-        <v>-0.7586181863638922</v>
+        <v>0.5596324445727963</v>
       </c>
       <c r="G44">
-        <v>-13.08315855666215</v>
+        <v>-11.5781635081798</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.76909684896565</v>
       </c>
       <c r="E45">
-        <v>-29.10021294735589</v>
+        <v>-25.86281794534264</v>
       </c>
       <c r="F45">
-        <v>0.2445513057743651</v>
+        <v>0.6485991036334632</v>
       </c>
       <c r="G45">
-        <v>-13.21705581450658</v>
+        <v>-11.71601734945206</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.07852873064182</v>
       </c>
       <c r="E46">
-        <v>-26.73978512942549</v>
+        <v>-25.80775882280939</v>
       </c>
       <c r="F46">
-        <v>-0.3607433823904561</v>
+        <v>0.7936147579023503</v>
       </c>
       <c r="G46">
-        <v>-13.0501221946062</v>
+        <v>-11.90495693551093</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.41757483811132</v>
       </c>
       <c r="E47">
-        <v>-29.35481103138487</v>
+        <v>-25.1225993973411</v>
       </c>
       <c r="F47">
-        <v>-0.1875342435672878</v>
+        <v>0.8939300503813703</v>
       </c>
       <c r="G47">
-        <v>-13.28543904758161</v>
+        <v>-12.40662847853319</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.76398958739299</v>
       </c>
       <c r="E48">
-        <v>-28.25243037925262</v>
+        <v>-24.81150725626615</v>
       </c>
       <c r="F48">
-        <v>-0.3292331147553657</v>
+        <v>0.7033127705883705</v>
       </c>
       <c r="G48">
-        <v>-14.23817807121658</v>
+        <v>-11.82296389088243</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.1190719668491</v>
       </c>
       <c r="E49">
-        <v>-27.72761813661331</v>
+        <v>-24.56820383043504</v>
       </c>
       <c r="F49">
-        <v>-0.04451329800434198</v>
+        <v>0.5295685064229938</v>
       </c>
       <c r="G49">
-        <v>-13.38593052301044</v>
+        <v>-12.5578336676444</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.45557806265414</v>
       </c>
       <c r="E50">
-        <v>-27.2755037050038</v>
+        <v>-23.58766801554495</v>
       </c>
       <c r="F50">
-        <v>-0.08759088805212467</v>
+        <v>0.8275347463121844</v>
       </c>
       <c r="G50">
-        <v>-13.43201799727737</v>
+        <v>-12.21399207813331</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.77241889124613</v>
       </c>
       <c r="E51">
-        <v>-25.49547055687288</v>
+        <v>-23.4251030178685</v>
       </c>
       <c r="F51">
-        <v>-0.03546172739395179</v>
+        <v>0.7655281327430302</v>
       </c>
       <c r="G51">
-        <v>-13.69787403510732</v>
+        <v>-12.0102273789138</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.05168166861971</v>
       </c>
       <c r="E52">
-        <v>-25.88220513580695</v>
+        <v>-22.8888154523387</v>
       </c>
       <c r="F52">
-        <v>-0.5050424988559216</v>
+        <v>0.6208686764573469</v>
       </c>
       <c r="G52">
-        <v>-13.80796130228079</v>
+        <v>-12.43796394048803</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.29112001882299</v>
       </c>
       <c r="E53">
-        <v>-26.02998470116699</v>
+        <v>-22.05668218450737</v>
       </c>
       <c r="F53">
-        <v>-0.3859746251123262</v>
+        <v>0.5868890455945112</v>
       </c>
       <c r="G53">
-        <v>-13.73678326712098</v>
+        <v>-12.29133147052815</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.48579138841274</v>
       </c>
       <c r="E54">
-        <v>-23.05126000688671</v>
+        <v>-21.83172349309804</v>
       </c>
       <c r="F54">
-        <v>-0.2705532246758543</v>
+        <v>0.6469788169935873</v>
       </c>
       <c r="G54">
-        <v>-14.42559559317883</v>
+        <v>-12.27997473155681</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.6318928190067</v>
       </c>
       <c r="E55">
-        <v>-25.95790987183592</v>
+        <v>-21.27261818454962</v>
       </c>
       <c r="F55">
-        <v>-0.3319344208558949</v>
+        <v>0.4714179431138713</v>
       </c>
       <c r="G55">
-        <v>-14.14747819337671</v>
+        <v>-12.94520289635084</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.73536347209848</v>
       </c>
       <c r="E56">
-        <v>-24.67449281466005</v>
+        <v>-22.05928209479672</v>
       </c>
       <c r="F56">
-        <v>-1.205548907931115</v>
+        <v>0.4658562843714754</v>
       </c>
       <c r="G56">
-        <v>-14.33571157302368</v>
+        <v>-12.83122953585349</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.78761420646838</v>
       </c>
       <c r="E57">
-        <v>-25.77592861121591</v>
+        <v>-20.50378401052001</v>
       </c>
       <c r="F57">
-        <v>-0.7818986238521695</v>
+        <v>0.6855558869419603</v>
       </c>
       <c r="G57">
-        <v>-13.42610988226768</v>
+        <v>-13.15692383971176</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.80293353254246</v>
       </c>
       <c r="E58">
-        <v>-24.29421232612478</v>
+        <v>-20.35673956356445</v>
       </c>
       <c r="F58">
-        <v>-0.1522507624124457</v>
+        <v>0.1545657548082548</v>
       </c>
       <c r="G58">
-        <v>-14.93599485536918</v>
+        <v>-12.10340224262604</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.77149244236775</v>
       </c>
       <c r="E59">
-        <v>-24.26494049270739</v>
+        <v>-19.92394171782672</v>
       </c>
       <c r="F59">
-        <v>-0.0798572499795885</v>
+        <v>0.3872649270308723</v>
       </c>
       <c r="G59">
-        <v>-14.44870068281018</v>
+        <v>-13.04743704379424</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.71425307510603</v>
       </c>
       <c r="E60">
-        <v>-23.68466626603632</v>
+        <v>-20.51537977653893</v>
       </c>
       <c r="F60">
-        <v>-0.4760869162910648</v>
+        <v>0.5174238119305502</v>
       </c>
       <c r="G60">
-        <v>-13.45299271932237</v>
+        <v>-13.12611444279203</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.62548211859298</v>
       </c>
       <c r="E61">
-        <v>-23.20219185964231</v>
+        <v>-19.59754083980845</v>
       </c>
       <c r="F61">
-        <v>-1.30589236490183</v>
+        <v>0.3090695293088074</v>
       </c>
       <c r="G61">
-        <v>-13.33839147475086</v>
+        <v>-12.64400912510787</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.52417236063782</v>
       </c>
       <c r="E62">
-        <v>-23.51083775924694</v>
+        <v>-19.79959457076135</v>
       </c>
       <c r="F62">
-        <v>-1.132758607512317</v>
+        <v>0.3274924203470684</v>
       </c>
       <c r="G62">
-        <v>-14.2733069450623</v>
+        <v>-12.86282085077826</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.40920726592685</v>
       </c>
       <c r="E63">
-        <v>-23.41267245637329</v>
+        <v>-19.35510958835555</v>
       </c>
       <c r="F63">
-        <v>-0.8734854090078913</v>
+        <v>0.09849025184314507</v>
       </c>
       <c r="G63">
-        <v>-14.17097620006903</v>
+        <v>-13.07238792985151</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.28906716883759</v>
       </c>
       <c r="E64">
-        <v>-20.90490531348327</v>
+        <v>-19.27488615840517</v>
       </c>
       <c r="F64">
-        <v>-0.6476086707147305</v>
+        <v>0.1226553857176122</v>
       </c>
       <c r="G64">
-        <v>-14.28712561618307</v>
+        <v>-12.75154830556042</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.16427611683475</v>
       </c>
       <c r="E65">
-        <v>-23.44051558509495</v>
+        <v>-19.11068479546675</v>
       </c>
       <c r="F65">
-        <v>-0.6569543117531145</v>
+        <v>0.255719355098908</v>
       </c>
       <c r="G65">
-        <v>-13.49634413325781</v>
+        <v>-13.09697331166602</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.02986205715822</v>
       </c>
       <c r="E66">
-        <v>-23.3689142218549</v>
+        <v>-18.45386273086776</v>
       </c>
       <c r="F66">
-        <v>-1.137561481713748</v>
+        <v>0.3639356158658298</v>
       </c>
       <c r="G66">
-        <v>-13.90609135922697</v>
+        <v>-13.00113548847085</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.8917632406795</v>
       </c>
       <c r="E67">
-        <v>-23.39504622751072</v>
+        <v>-18.57148998200955</v>
       </c>
       <c r="F67">
-        <v>0.02382038578739483</v>
+        <v>-0.0128174760710245</v>
       </c>
       <c r="G67">
-        <v>-14.35122983887326</v>
+        <v>-12.99911216141273</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.73918224535405</v>
       </c>
       <c r="E68">
-        <v>-21.53518005129395</v>
+        <v>-18.81530840604494</v>
       </c>
       <c r="F68">
-        <v>-1.338481995262768</v>
+        <v>-0.0242075278595177</v>
       </c>
       <c r="G68">
-        <v>-14.96202136819799</v>
+        <v>-13.22556031501213</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.58612130638491</v>
       </c>
       <c r="E69">
-        <v>-21.02331336835413</v>
+        <v>-18.37222720906693</v>
       </c>
       <c r="F69">
-        <v>-0.3197176583994077</v>
+        <v>0.0156642803394309</v>
       </c>
       <c r="G69">
-        <v>-13.68348752703799</v>
+        <v>-12.95291634124528</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.4191709896467</v>
       </c>
       <c r="E70">
-        <v>-20.16713716016338</v>
+        <v>-18.69346564540844</v>
       </c>
       <c r="F70">
-        <v>-1.615427583938519</v>
+        <v>-0.1010725675326866</v>
       </c>
       <c r="G70">
-        <v>-14.70858594776026</v>
+        <v>-13.26363933024581</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.25534190535861</v>
       </c>
       <c r="E71">
-        <v>-20.87128922102011</v>
+        <v>-18.76131250561084</v>
       </c>
       <c r="F71">
-        <v>-0.2195597557269195</v>
+        <v>0.09807606814174531</v>
       </c>
       <c r="G71">
-        <v>-13.6489643459374</v>
+        <v>-12.58463948773366</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.08385613442462</v>
       </c>
       <c r="E72">
-        <v>-21.57420777811337</v>
+        <v>-18.67043193540094</v>
       </c>
       <c r="F72">
-        <v>-1.229459733012923</v>
+        <v>-0.2190221452825026</v>
       </c>
       <c r="G72">
-        <v>-14.322281902847</v>
+        <v>-12.66352705167103</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.91961129137946</v>
       </c>
       <c r="E73">
-        <v>-22.71637827134314</v>
+        <v>-18.66279833298591</v>
       </c>
       <c r="F73">
-        <v>-0.7737648843240812</v>
+        <v>-0.01058088408346584</v>
       </c>
       <c r="G73">
-        <v>-14.90433566108504</v>
+        <v>-12.9287917558511</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.75921705873359</v>
       </c>
       <c r="E74">
-        <v>-22.75104927948281</v>
+        <v>-19.29685664631351</v>
       </c>
       <c r="F74">
-        <v>-1.262464375442663</v>
+        <v>-0.4047073255592342</v>
       </c>
       <c r="G74">
-        <v>-14.1312054223403</v>
+        <v>-13.02515433870909</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.61214646042226</v>
       </c>
       <c r="E75">
-        <v>-20.65823363326773</v>
+        <v>-19.02172300888892</v>
       </c>
       <c r="F75">
-        <v>-0.24154214149501</v>
+        <v>-0.191532773020601</v>
       </c>
       <c r="G75">
-        <v>-13.34609317129465</v>
+        <v>-12.60321493549943</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.48226719066336</v>
       </c>
       <c r="E76">
-        <v>-22.50999274097844</v>
+        <v>-19.15534843005395</v>
       </c>
       <c r="F76">
-        <v>-1.156401041555618</v>
+        <v>-0.3240127433829232</v>
       </c>
       <c r="G76">
-        <v>-14.63208852049605</v>
+        <v>-12.23115380770299</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.36987126704228</v>
       </c>
       <c r="E77">
-        <v>-23.73506133225179</v>
+        <v>-19.33988806885006</v>
       </c>
       <c r="F77">
-        <v>-1.365471861980782</v>
+        <v>-0.007848928389033068</v>
       </c>
       <c r="G77">
-        <v>-13.85979894150964</v>
+        <v>-12.46624222052667</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.28246124515733</v>
       </c>
       <c r="E78">
-        <v>-23.74593028628886</v>
+        <v>-20.02211532712302</v>
       </c>
       <c r="F78">
-        <v>-0.9312441545354896</v>
+        <v>-0.1675233722178602</v>
       </c>
       <c r="G78">
-        <v>-13.7314286299646</v>
+        <v>-12.11913458953209</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.21124195484993</v>
       </c>
       <c r="E79">
-        <v>-24.51421208321227</v>
+        <v>-19.73210073352157</v>
       </c>
       <c r="F79">
-        <v>-1.19615273648116</v>
+        <v>-0.7303526338455675</v>
       </c>
       <c r="G79">
-        <v>-13.3765723090236</v>
+        <v>-11.81963780227335</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.166871963916</v>
       </c>
       <c r="E80">
-        <v>-24.16747708254763</v>
+        <v>-20.89196390699511</v>
       </c>
       <c r="F80">
-        <v>-1.592391514834067</v>
+        <v>-0.5313804404279319</v>
       </c>
       <c r="G80">
-        <v>-13.48945437828186</v>
+        <v>-12.06827206340802</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.13289706827227</v>
       </c>
       <c r="E81">
-        <v>-24.43309986603837</v>
+        <v>-21.46766544799754</v>
       </c>
       <c r="F81">
-        <v>-1.383930372817363</v>
+        <v>-0.2797770957060268</v>
       </c>
       <c r="G81">
-        <v>-14.06117089331139</v>
+        <v>-11.65569087418521</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.12030726200619</v>
       </c>
       <c r="E82">
-        <v>-24.47115158819645</v>
+        <v>-21.70929928287606</v>
       </c>
       <c r="F82">
-        <v>-1.043868158252708</v>
+        <v>-0.7255191100502324</v>
       </c>
       <c r="G82">
-        <v>-13.4862405516902</v>
+        <v>-11.65217159047639</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.11193313096085</v>
       </c>
       <c r="E83">
-        <v>-24.9930275104291</v>
+        <v>-22.43599082159264</v>
       </c>
       <c r="F83">
-        <v>-1.083199042537628</v>
+        <v>-0.601753564765361</v>
       </c>
       <c r="G83">
-        <v>-14.7979399867634</v>
+        <v>-11.58801123677748</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.11741323454959</v>
       </c>
       <c r="E84">
-        <v>-25.5314539797912</v>
+        <v>-23.3912626519938</v>
       </c>
       <c r="F84">
-        <v>-0.5655713049784814</v>
+        <v>-0.6175687552196092</v>
       </c>
       <c r="G84">
-        <v>-14.37642091343291</v>
+        <v>-11.4672029469406</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.12665568060364</v>
       </c>
       <c r="E85">
-        <v>-27.39315587541354</v>
+        <v>-24.14243321825892</v>
       </c>
       <c r="F85">
-        <v>-1.125515362942238</v>
+        <v>-0.7007252453170404</v>
       </c>
       <c r="G85">
-        <v>-13.7971175746216</v>
+        <v>-11.05886813379523</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.14329964906624</v>
       </c>
       <c r="E86">
-        <v>-28.63583408270416</v>
+        <v>-25.65276097616679</v>
       </c>
       <c r="F86">
-        <v>-1.316483042146622</v>
+        <v>-0.7018634221284868</v>
       </c>
       <c r="G86">
-        <v>-13.07830909858416</v>
+        <v>-11.32666917634556</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.16308664572455</v>
       </c>
       <c r="E87">
-        <v>-27.11263136968932</v>
+        <v>-25.50177097845265</v>
       </c>
       <c r="F87">
-        <v>-1.829540676744524</v>
+        <v>-0.5668925509859466</v>
       </c>
       <c r="G87">
-        <v>-14.09165003104034</v>
+        <v>-11.20134429836606</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.18131608505051</v>
       </c>
       <c r="E88">
-        <v>-30.41515287848721</v>
+        <v>-27.29833390765638</v>
       </c>
       <c r="F88">
-        <v>-1.080453004597348</v>
+        <v>-0.6968526277089526</v>
       </c>
       <c r="G88">
-        <v>-13.18869007452413</v>
+        <v>-10.83076476812507</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.19830734639797</v>
       </c>
       <c r="E89">
-        <v>-30.89992816395517</v>
+        <v>-27.52262808525375</v>
       </c>
       <c r="F89">
-        <v>-0.4210634399275104</v>
+        <v>-0.9469193508986646</v>
       </c>
       <c r="G89">
-        <v>-13.95342807478074</v>
+        <v>-10.74959541341507</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.20339618599843</v>
       </c>
       <c r="E90">
-        <v>-31.13670897140063</v>
+        <v>-29.21523405839136</v>
       </c>
       <c r="F90">
-        <v>-1.248419406128198</v>
+        <v>-0.8119940399632783</v>
       </c>
       <c r="G90">
-        <v>-13.71110659406738</v>
+        <v>-10.84213847693626</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.20570742439472</v>
       </c>
       <c r="E91">
-        <v>-33.07557961004395</v>
+        <v>-30.49367556840008</v>
       </c>
       <c r="F91">
-        <v>-1.209571460039109</v>
+        <v>-0.9633872948663188</v>
       </c>
       <c r="G91">
-        <v>-14.93215706082024</v>
+        <v>-11.26919102342761</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.19330205465264</v>
       </c>
       <c r="E92">
-        <v>-32.64055771964178</v>
+        <v>-31.69444372021186</v>
       </c>
       <c r="F92">
-        <v>-1.344671556496486</v>
+        <v>-1.061779118236039</v>
       </c>
       <c r="G92">
-        <v>-13.4683491190073</v>
+        <v>-10.79320398569273</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.18283538787768</v>
       </c>
       <c r="E93">
-        <v>-35.06755528529219</v>
+        <v>-33.42489375494131</v>
       </c>
       <c r="F93">
-        <v>-1.528816801771414</v>
+        <v>-1.183931832187659</v>
       </c>
       <c r="G93">
-        <v>-13.78820057647066</v>
+        <v>-10.9028800605931</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.16401102038091</v>
       </c>
       <c r="E94">
-        <v>-37.10412399053511</v>
+        <v>-35.30891500822328</v>
       </c>
       <c r="F94">
-        <v>-1.568396196277174</v>
+        <v>-0.9733310171695241</v>
       </c>
       <c r="G94">
-        <v>-13.98236165171175</v>
+        <v>-11.50708990280363</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.15268281260563</v>
       </c>
       <c r="E95">
-        <v>-39.16598575274624</v>
+        <v>-37.58855455946312</v>
       </c>
       <c r="F95">
-        <v>-1.312848165983138</v>
+        <v>-1.214580597723838</v>
       </c>
       <c r="G95">
-        <v>-14.10627542223976</v>
+        <v>-11.87806365547787</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.14476842213988</v>
       </c>
       <c r="E96">
-        <v>-41.35864044599887</v>
+        <v>-38.24052359662904</v>
       </c>
       <c r="F96">
-        <v>-1.936940995619688</v>
+        <v>-1.496262791208796</v>
       </c>
       <c r="G96">
-        <v>-14.43169820866055</v>
+        <v>-11.6697053511503</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.14857061673558</v>
       </c>
       <c r="E97">
-        <v>-43.4407408069959</v>
+        <v>-40.72542108135889</v>
       </c>
       <c r="F97">
-        <v>-2.041724501869409</v>
+        <v>-1.719445678708053</v>
       </c>
       <c r="G97">
-        <v>-13.86218646743822</v>
+        <v>-12.26887776167228</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.16758280055024</v>
       </c>
       <c r="E98">
-        <v>-45.06868543301725</v>
+        <v>-43.17747081772067</v>
       </c>
       <c r="F98">
-        <v>-2.88545066468422</v>
+        <v>-1.655759136046021</v>
       </c>
       <c r="G98">
-        <v>-13.37633864738269</v>
+        <v>-12.24625696516258</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.19689079721457</v>
       </c>
       <c r="E99">
-        <v>-45.59718468901018</v>
+        <v>-43.95613148974483</v>
       </c>
       <c r="F99">
-        <v>-2.531037813233465</v>
+        <v>-1.848848264168975</v>
       </c>
       <c r="G99">
-        <v>-13.66398787568696</v>
+        <v>-12.06719513126419</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.24811232564071</v>
       </c>
       <c r="E100">
-        <v>-48.36752511997567</v>
+        <v>-47.34873511387541</v>
       </c>
       <c r="F100">
-        <v>-2.627338837278519</v>
+        <v>-1.910254311371099</v>
       </c>
       <c r="G100">
-        <v>-14.36527956089034</v>
+        <v>-12.16627027775234</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.30020902861111</v>
       </c>
       <c r="E101">
-        <v>-49.90804360930656</v>
+        <v>-47.9845128566915</v>
       </c>
       <c r="F101">
-        <v>-2.814558982352638</v>
+        <v>-2.036750983983</v>
       </c>
       <c r="G101">
-        <v>-14.79841905839587</v>
+        <v>-12.30505093335445</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.38516165403578</v>
       </c>
       <c r="E102">
-        <v>-51.56345861333316</v>
+        <v>-50.53399277752243</v>
       </c>
       <c r="F102">
-        <v>-2.28970208246926</v>
+        <v>-2.323253447384849</v>
       </c>
       <c r="G102">
-        <v>-14.78058767283857</v>
+        <v>-12.92494482369609</v>
       </c>
     </row>
   </sheetData>
